--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,12 +840,101 @@
           <t>NSE:HAL26AUG4850CE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:18:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4075.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K5" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="L5" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="S5" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="U5" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:SIEMENS26AUG4100CE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,11 @@
           <t>NSE:VMM26AUG112.5PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:19:38</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -929,12 +934,278 @@
           <t>NSE:SIEMENS26AUG4100CE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:19:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:19:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5558.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I6" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K6" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="L6" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="M6" t="n">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2544</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="S6" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:KEI26AUG5600CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:19:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>398.65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>400</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35714</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="S7" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="U7" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:NATIONALUM26AUG400CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:19:38</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1051</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1060</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20833</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="S8" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="U8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:HINDALCO26AUG1060CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,6 +1206,101 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:22:52</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>377.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H9" t="n">
+        <v>376</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>71428</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="U9" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:INDUSTOWER26AUG376PE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -934,11 +934,7 @@
           <t>NSE:SIEMENS26AUG4100CE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:19:38</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1295,12 +1291,6 @@
           <t>NSE:INDUSTOWER26AUG376PE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -934,7 +934,11 @@
           <t>NSE:SIEMENS26AUG4100CE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:26:13</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,6 +1295,101 @@
           <t>NSE:INDUSTOWER26AUG376PE</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:27:49</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>8578.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8600</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="L10" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="M10" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1610</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S10" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:DIVISLAB26AUG8600CE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1384,12 +1384,11 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:26</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1389,6 +1389,101 @@
           <t>2026-08-25 09:29:26</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>512.35</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H11" t="n">
+        <v>510</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11904</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="S11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG510CE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1028,6 +1028,11 @@
           <t>NSE:KEI26AUG5600CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:32:38</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1206,6 +1211,11 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:32:38</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1478,12 +1488,11 @@
           <t>NSE:JUBLFOOD26AUG510CE</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:32:38</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -845,6 +845,11 @@
           <t>NSE:HAL26AUG4850CE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:35:48</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,11 +1216,7 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:32:38</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,7 +1216,11 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:45:16</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -845,11 +845,7 @@
           <t>NSE:HAL26AUG4850CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:35:48</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1214,11 +1210,6 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:HINDALCO26AUG1060CE</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:45:16</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,6 +756,11 @@
           <t>NSE:DIXON26AUG14500CE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:48:27</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -845,7 +850,6 @@
           <t>NSE:HAL26AUG4850CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1487,6 +1491,95 @@
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-08-25 09:32:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:48:27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1270.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="L12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6944</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="S12" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="U12" t="n">
+        <v>32</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1582,6 +1582,11 @@
           <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:50:04</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1582,11 +1582,7 @@
           <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-25 09:50:04</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,6 +1216,11 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:12:13</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1582,7 +1587,6 @@
           <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,101 @@
           <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:13:48</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4065.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K13" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="L13" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="S13" t="n">
+        <v>16</v>
+      </c>
+      <c r="T13" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="U13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:SIEMENS26AUG4100CE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1310,6 +1310,11 @@
           <t>NSE:INDUSTOWER26AUG376PE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:15:24</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1676,12 +1681,6 @@
           <t>NSE:SIEMENS26AUG4100CE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1681,6 +1681,11 @@
           <t>NSE:SIEMENS26AUG4100CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:16:58</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1310,6 +1310,16 @@
           <t>NSE:INDUSTOWER26AUG376PE</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:18:33</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>2026-08-25 10:15:24</t>
@@ -1679,11 +1689,6 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:SIEMENS26AUG4100CE</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:16:58</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1216,11 +1216,6 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:12:13</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1689,6 +1684,189 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:SIEMENS26AUG4100CE</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:21:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:21:43</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>294</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>295</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17241</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="S14" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>33</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:ANGELONE26AUG295PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:21:43</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1311.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>29411</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="U15" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NSE:JSWSTEEL26AUG1320CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1780,6 +1780,11 @@
           <t>NSE:ANGELONE26AUG295PE</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:23:22</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1867,6 +1872,11 @@
       <c r="W15" t="inlineStr">
         <is>
           <t>NSE:JSWSTEEL26AUG1320CE</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:23:22</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1874,9 +1874,94 @@
           <t>NSE:JSWSTEEL26AUG1320CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:23:22</t>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:24:59</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5610</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K16" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="L16" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="M16" t="n">
+        <v>120.66</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3086</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="U16" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1597,6 +1597,11 @@
           <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:26:35</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1780,11 +1785,6 @@
           <t>NSE:ANGELONE26AUG295PE</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:23:22</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1874,7 +1874,6 @@
           <t>NSE:JSWSTEEL26AUG1320CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1597,11 +1597,7 @@
           <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:26:35</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1597,7 +1597,6 @@
           <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1868,6 +1867,11 @@
       <c r="W15" t="inlineStr">
         <is>
           <t>NSE:JSWSTEEL26AUG1320CE</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:29:47</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1780,6 +1780,11 @@
           <t>NSE:ANGELONE26AUG295PE</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:31:23</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1874,11 +1874,7 @@
           <t>NSE:JSWSTEEL26AUG1320CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:29:47</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,6 +1216,11 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:36:09</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1874,7 +1879,11 @@
           <t>NSE:JSWSTEEL26AUG1320CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:36:09</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,11 +1216,6 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:36:09</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1600,6 +1595,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:LODHA26AUG1280CE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:37:44</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,6 +1216,11 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:40:54</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,11 +1216,7 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:40:54</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,7 +1216,11 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:48:50</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1216,11 +1216,7 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-25 10:48:50</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,6 +850,11 @@
           <t>NSE:HAL26AUG4850CE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:21:03</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1216,7 +1221,11 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:21:03</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1972,6 +1981,456 @@
       <c r="W16" t="inlineStr">
         <is>
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:21:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:21:03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N17" t="n">
+        <v>277777</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="S17" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>79.58</v>
+      </c>
+      <c r="U17" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NSE:IDEA26AUG15CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:21:03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1843</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1840</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K18" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10526</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>NSE:LAURUSLABS26AUG1840CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:21:03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1138.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1140</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>15151</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="S19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>NSE:AUBANK26AUG1140CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:21:03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>334.55</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H20" t="n">
+        <v>335</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>83333</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="S20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="U20" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>NSE:NYKAA26AUG335CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:21:03</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>803.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="H21" t="n">
+        <v>800</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K21" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="L21" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="M21" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7407</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="S21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="U21" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26AUG800CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2433,6 +2433,11 @@
           <t>NSE:SONACOMS26AUG800CE</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:22:43</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2438,6 +2438,190 @@
           <t>2026-08-25 12:22:43</t>
         </is>
       </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:24:20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>8604.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8600</v>
+      </c>
+      <c r="I22" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K22" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="L22" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="M22" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1610</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="U22" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NSE:DIVISLAB26AUG8600CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:24:20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1274</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K23" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17</v>
+      </c>
+      <c r="M23" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6944</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="S23" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T23" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>NSE:LODHA26AUG1280CE</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2616,12 +2616,11 @@
           <t>NSE:LODHA26AUG1280CE</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:26:01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,101 @@
           <t>2026-08-25 12:26:01</t>
         </is>
       </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:27:37</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>470.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>470</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="N24" t="n">
+        <v>17543</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="S24" t="n">
+        <v>21</v>
+      </c>
+      <c r="T24" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="U24" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>NSE:OIL26AUG470CE</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2527,6 +2527,11 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:29:13</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2710,12 +2715,6 @@
           <t>NSE:OIL26AUG470CE</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2344,6 +2344,11 @@
           <t>NSE:NYKAA26AUG335CE</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:30:48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2532,11 +2532,7 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-25 12:29:13</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2532,7 +2532,11 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:43:31</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1983,11 +1983,7 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-25 12:21:03</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1983,7 +1983,11 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:56:12</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1795,6 +1795,16 @@
           <t>NSE:ANGELONE26AUG295PE</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:59:18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>2026-08-25 10:31:23</t>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1993,11 +1993,7 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-25 12:56:12</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1993,7 +1993,6 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2348,6 +2347,16 @@
       <c r="W20" t="inlineStr">
         <is>
           <t>NSE:NYKAA26AUG335CE</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:02:18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1993,6 +1993,11 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:02:32</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1132,6 +1132,16 @@
           <t>NSE:NATIONALUM26AUG400CE</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:02:48</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2003,11 +2003,6 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:02:32</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2562,11 +2557,7 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-25 12:43:31</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2003,6 +2003,11 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:05:44</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2557,7 +2562,11 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:05:44</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -756,6 +756,16 @@
           <t>NSE:DIXON26AUG14500CE</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:07:48</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-25 09:48:27</t>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -761,9 +761,14 @@
           <t>2026-08-25 13:07:48</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:09:18</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1924,6 +1924,16 @@
           <t>NSE:JSWSTEEL26AUG1320CE</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:10:19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-25 10:36:09</t>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2028,11 +2028,7 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:05:44</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -766,9 +766,14 @@
           <t>2026-08-25 13:09:18</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:16:19</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2028,7 +2033,6 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,6 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:16:53</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1548,6 +1548,16 @@
           <t>NSE:JUBLFOOD26AUG510CE</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:17:18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-08-25 09:32:38</t>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,11 +1162,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:16:53</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2135,6 +2130,11 @@
       <c r="W17" t="inlineStr">
         <is>
           <t>NSE:IDEA26AUG15CE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:18:30</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,6 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:20:06</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2043,6 +2048,16 @@
           <t>NSE:HEROMOTOCO26AUG5600CE</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:20:06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2130,11 +2145,6 @@
       <c r="W17" t="inlineStr">
         <is>
           <t>NSE:IDEA26AUG15CE</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:18:30</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,11 +1162,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:20:06</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2056,6 +2051,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>SL Hit</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:21:41</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2612,11 +2612,7 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:05:44</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,6 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:28:02</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2612,7 +2617,6 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2241,6 +2241,16 @@
           <t>NSE:LAURUSLABS26AUG1840CE</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:29:18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1746,6 +1746,16 @@
           <t>NSE:SIEMENS26AUG4100CE</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:35:49</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-08-25 10:21:43</t>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,11 +1162,7 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:28:02</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,7 +1162,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1747,9 +1746,14 @@
           <t>2026-08-25 13:35:49</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:40:45</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2637,6 +2637,11 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:42:19</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1751,9 +1751,14 @@
           <t>2026-08-25 13:40:45</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:43:48</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2637,11 +2642,7 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:42:19</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2642,7 +2642,16 @@
           <t>NSE:DIVISLAB26AUG8600CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:49:18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,6 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:55:06</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,11 +1162,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:55:06</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2840,6 +2835,101 @@
           <t>NSE:OIL26AUG470CE</t>
         </is>
       </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:56:42</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1329.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1320</v>
+      </c>
+      <c r="I25" t="n">
+        <v>16</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K25" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="L25" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3125</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="T25" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="U25" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>NSE:NAUKRI26AUG1320CE</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,6 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:58:29</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2924,12 +2929,11 @@
           <t>NSE:NAUKRI26AUG1320CE</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2026-08-25 13:58:29</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,11 +1162,7 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-25 13:58:29</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,7 +1162,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2740,6 +2739,16 @@
       <c r="W23" t="inlineStr">
         <is>
           <t>NSE:LODHA26AUG1280CE</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:03:18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,6 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:05:03</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2657,6 +2657,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:08:20</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2172,6 +2172,11 @@
           <t>NSE:IDEA26AUG15CE</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:19:35</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1256,6 +1256,16 @@
           <t>NSE:HINDALCO26AUG1060CE</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:19:48</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>2026-08-25 12:21:03</t>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2182,11 +2182,7 @@
           <t>NSE:IDEA26AUG15CE</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:19:35</t>
-        </is>
-      </c>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2182,7 +2182,6 @@
           <t>NSE:IDEA26AUG15CE</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2864,6 +2863,16 @@
       <c r="W24" t="inlineStr">
         <is>
           <t>NSE:OIL26AUG470CE</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:22:18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2667,11 +2667,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:08:20</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,11 +1162,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:05:03</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2667,7 +2662,6 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2963,6 +2957,105 @@
       <c r="AC25" t="inlineStr">
         <is>
           <t>2026-08-25 13:58:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:25:57</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>5599.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K26" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="L26" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>142.21</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="S26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="T26" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="U26" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5600CE</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:25:59</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -3058,6 +3058,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:27:37</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2662,6 +2662,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:30:49</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2662,11 +2662,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:30:49</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2662,7 +2662,6 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3064,6 +3063,101 @@
           <t>2026-08-25 14:27:37</t>
         </is>
       </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:37:15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1707.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K27" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="L27" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="M27" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3816</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="S27" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="U27" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>NSE:PAYTM26AUG1700CE</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,6 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:38:53</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3152,12 +3157,6 @@
           <t>NSE:PAYTM26AUG1700CE</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,11 +1162,7 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:38:53</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,7 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:45:16</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,11 +1162,6 @@
           <t>SL Hit</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:45:16</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2665,6 +2660,11 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>Target 1 Hit</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:46:53</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2662,11 +2662,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:46:53</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2662,7 +2662,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:50:10</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2662,11 +2662,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-25 14:50:10</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1162,6 +1162,11 @@
           <t>SL Hit</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:58:16</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2657,12 +2662,16 @@
           <t>2026-08-25 13:49:18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:58:17</t>
+        </is>
+      </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr"/>
+          <t>Target 2 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -1058,6 +1058,16 @@
           <t>NSE:KEI26AUG5600CE</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:04:18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-25 09:32:38</t>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3172,6 +3172,101 @@
           <t>NSE:PAYTM26AUG1700CE</t>
         </is>
       </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:04:47</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="H28" t="n">
+        <v>350</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N28" t="n">
+        <v>333333</v>
+      </c>
+      <c r="O28" t="n">
+        <v>5</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="S28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="U28" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>NSE:FEDERALBNK26AUG350CE</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
+++ b/backend/signal_logs/2026-08-25/signals_2026-08-25.xlsx
@@ -2380,6 +2380,16 @@
           <t>NSE:AUBANK26AUG1140CE</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2026-08-25 17:52:16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2677,9 +2687,14 @@
           <t>2026-08-25 14:58:17</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-25 17:52:16</t>
+        </is>
+      </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
     </row>
@@ -3261,12 +3276,6 @@
           <t>NSE:FEDERALBNK26AUG350CE</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
